--- a/Excel/DropConfig.xlsx
+++ b/Excel/DropConfig.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView windowHeight="17680" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="普通装备" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="112">
   <si>
     <t>_id</t>
   </si>
@@ -457,6 +457,12 @@
     <t>20067,20068,20069,20070,20071,20072</t>
   </si>
   <si>
+    <t>天龙装备</t>
+  </si>
+  <si>
+    <t>20073,20074,20075,20076,20077,20078</t>
+  </si>
+  <si>
     <t>神兵符1-2</t>
   </si>
   <si>
@@ -644,6 +650,15 @@
   </si>
   <si>
     <t>50034,50035,50036</t>
+  </si>
+  <si>
+    <t>随机珍宝材料</t>
+  </si>
+  <si>
+    <t>25,25,3,3,1,1</t>
+  </si>
+  <si>
+    <t>50037,50038,50039,50040,50041,50042</t>
   </si>
 </sst>
 </file>
@@ -834,12 +849,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1637,7 +1652,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C2:H77"/>
+  <dimension ref="C2:H83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -2934,6 +2949,108 @@
       </c>
       <c r="H77" s="9" t="s">
         <v>43</v>
+      </c>
+    </row>
+    <row r="78" customHeight="1" spans="3:8">
+      <c r="C78" s="1">
+        <v>2073</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E78" s="1">
+        <v>2</v>
+      </c>
+      <c r="G78" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H78" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" customHeight="1" spans="3:8">
+      <c r="C79" s="1">
+        <v>2074</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E79" s="1">
+        <v>2</v>
+      </c>
+      <c r="G79" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" customHeight="1" spans="3:8">
+      <c r="C80" s="1">
+        <v>2075</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E80" s="1">
+        <v>2</v>
+      </c>
+      <c r="G80" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="H80" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" customHeight="1" spans="3:8">
+      <c r="C81" s="1">
+        <v>2076</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E81" s="1">
+        <v>2</v>
+      </c>
+      <c r="G81" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" customHeight="1" spans="3:8">
+      <c r="C82" s="1">
+        <v>2077</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E82" s="1">
+        <v>2</v>
+      </c>
+      <c r="G82" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="H82" s="9" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" customHeight="1" spans="3:8">
+      <c r="C83" s="1">
+        <v>2078</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E83" s="1">
+        <v>2</v>
+      </c>
+      <c r="G83" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="H83" s="9" t="s">
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -3036,16 +3153,16 @@
         <v>3001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1">
         <v>5</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="3:8">
@@ -3053,16 +3170,16 @@
         <v>3002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1">
         <v>5</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -3070,16 +3187,16 @@
         <v>3003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E8" s="1">
         <v>5</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -3087,16 +3204,16 @@
         <v>3004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E9" s="1">
         <v>5</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -3243,16 +3360,16 @@
         <v>4001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E6" s="1">
         <v>4</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3260,16 +3377,16 @@
         <v>4002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E7" s="1">
         <v>4</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3277,16 +3394,16 @@
         <v>4003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E8" s="1">
         <v>4</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3294,16 +3411,16 @@
         <v>4004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E9" s="1">
         <v>4</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="10" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3311,16 +3428,16 @@
         <v>4005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E10" s="1">
         <v>4</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3328,16 +3445,16 @@
         <v>4006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E11" s="1">
         <v>4</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="12" s="1" customFormat="1" customHeight="1" spans="1:8">
@@ -3345,56 +3462,56 @@
         <v>4007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E12" s="1">
         <v>4</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" s="1" customFormat="1" customHeight="1" spans="1:8">
       <c r="A13" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C13" s="6">
         <v>4008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E13" s="1">
         <v>4</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="1:8">
       <c r="A14" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C14" s="6">
         <v>4009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E14" s="1">
         <v>4</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16" ht="32" customHeight="1"/>
@@ -3423,7 +3540,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C1:H17"/>
+  <dimension ref="C1:H18"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -3431,7 +3548,7 @@
     <col min="4" max="4" width="13.875" style="1" customWidth="1"/>
     <col min="5" max="6" width="14.25" style="1" customWidth="1"/>
     <col min="7" max="7" width="15.4166666666667" style="1" customWidth="1"/>
-    <col min="8" max="8" width="19.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.1666666666667" style="2" customWidth="1"/>
     <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -3507,16 +3624,16 @@
         <v>5001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E6" s="1">
         <v>6</v>
       </c>
       <c r="G6" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H6" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" customHeight="1" spans="3:8">
@@ -3524,16 +3641,16 @@
         <v>5002</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E7" s="1">
         <v>6</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="3:8">
@@ -3541,16 +3658,16 @@
         <v>5003</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E8" s="1">
         <v>6</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="3:8">
@@ -3558,16 +3675,16 @@
         <v>5004</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E9" s="1">
         <v>6</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" customHeight="1" spans="3:8">
@@ -3575,16 +3692,16 @@
         <v>5005</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E10" s="1">
         <v>6</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:8">
@@ -3592,16 +3709,16 @@
         <v>5006</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E11" s="1">
         <v>6</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H11" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:8">
@@ -3609,16 +3726,16 @@
         <v>5007</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E12" s="1">
         <v>6</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H12" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:8">
@@ -3626,16 +3743,16 @@
         <v>5008</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E13" s="1">
         <v>6</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H13" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14" customHeight="1" spans="3:8">
@@ -3643,16 +3760,16 @@
         <v>5009</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E14" s="1">
         <v>6</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" customHeight="1" spans="3:8">
@@ -3660,16 +3777,16 @@
         <v>5010</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E15" s="1">
         <v>6</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" customHeight="1" spans="3:8">
@@ -3677,16 +3794,16 @@
         <v>5011</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E16" s="1">
         <v>6</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H16" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" customHeight="1" spans="3:8">
@@ -3694,16 +3811,33 @@
         <v>5012</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E17" s="1">
         <v>6</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="H17" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:8">
+      <c r="C18" s="6">
+        <v>5013</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" s="1">
+        <v>6</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>110</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
